--- a/data/trans_orig/P2A_senso_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>460133</t>
+          <t>459940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471296</t>
+          <t>471164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294150</t>
+          <t>293347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303798</t>
+          <t>303766</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>759089</t>
+          <t>758767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773671</t>
+          <t>773438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>915</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17766</t>
+          <t>17641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353592</t>
+          <t>353754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363959</t>
+          <t>364074</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>362402</t>
+          <t>363716</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370939</t>
+          <t>370950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>721033</t>
+          <t>721158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733908</t>
+          <t>733811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>14624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531334</t>
+          <t>531350</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540535</t>
+          <t>540520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158480</t>
+          <t>159232</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166851</t>
+          <t>166831</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>694572</t>
+          <t>695547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>706595</t>
+          <t>706954</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32157</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18256</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>23270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43737</t>
+          <t>47372</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1206177</t>
+          <t>1205358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1224775</t>
+          <t>1224515</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>696029</t>
+          <t>696279</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>709235</t>
+          <t>709056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1908883</t>
+          <t>1905248</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1931211</t>
+          <t>1929350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>334425</t>
+          <t>334054</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346889</t>
+          <t>346776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>554820</t>
+          <t>554399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>565524</t>
+          <t>565587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>894753</t>
+          <t>894628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>910707</t>
+          <t>910651</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>16248</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37185</t>
+          <t>37256</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39514</t>
+          <t>40164</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289807</t>
+          <t>289452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1211575</t>
+          <t>1211504</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1231776</t>
+          <t>1232512</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1507446</t>
+          <t>1506796</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1529223</t>
+          <t>1528386</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>37639</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68772</t>
+          <t>67095</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44180</t>
+          <t>42920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73082</t>
+          <t>74087</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,47 +2841,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>106733</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>87079</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>130229</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>106733</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>84652</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>126934</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3201418</t>
+          <t>3203095</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3230609</t>
+          <t>3232551</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3305042</t>
+          <t>3304037</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3333944</t>
+          <t>3335204</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,47 +2954,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6399</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6541581</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6518085</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6561235</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6399</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6541581</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6521380</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6563662</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>18722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30300</t>
+          <t>29286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421406</t>
+          <t>420798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434281</t>
+          <t>434112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294597</t>
+          <t>295732</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310030</t>
+          <t>310171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>721365</t>
+          <t>722379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741820</t>
+          <t>741399</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>13284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410744</t>
+          <t>411417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417938</t>
+          <t>418026</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326471</t>
+          <t>327598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336130</t>
+          <t>336915</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>742627</t>
+          <t>743524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>753674</t>
+          <t>753862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29901</t>
+          <t>30612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608502</t>
+          <t>606081</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623417</t>
+          <t>623099</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>248018</t>
+          <t>246928</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258093</t>
+          <t>257272</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>859643</t>
+          <t>858932</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878258</t>
+          <t>878197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35419</t>
+          <t>33980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31132</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30564</t>
+          <t>28486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57712</t>
+          <t>56428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1123590</t>
+          <t>1125029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144107</t>
+          <t>1144553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>735525</t>
+          <t>737194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>755184</t>
+          <t>755341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1867955</t>
+          <t>1869239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895103</t>
+          <t>1897181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24676</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31914</t>
+          <t>30520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>499116</t>
+          <t>498973</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508553</t>
+          <t>508534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>736846</t>
+          <t>737279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>753221</t>
+          <t>753305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1240204</t>
+          <t>1241598</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1259501</t>
+          <t>1260026</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>13849</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34568</t>
+          <t>35612</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18660</t>
+          <t>18741</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40363</t>
+          <t>40648</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253524</t>
+          <t>253033</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265825</t>
+          <t>264958</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1074783</t>
+          <t>1073739</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1095040</t>
+          <t>1094113</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1335870</t>
+          <t>1335585</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357573</t>
+          <t>1357492</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42414</t>
+          <t>43631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73441</t>
+          <t>76591</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59273</t>
+          <t>59959</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94783</t>
+          <t>94752</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108943</t>
+          <t>112766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>156620</t>
+          <t>159654</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3348469</t>
+          <t>3345319</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3379496</t>
+          <t>3378279</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3455342</t>
+          <t>3455373</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3490852</t>
+          <t>3490166</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6815415</t>
+          <t>6812381</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6863092</t>
+          <t>6859269</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421275</t>
+          <t>422042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428309</t>
+          <t>428310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>342222</t>
+          <t>342405</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>767761</t>
+          <t>768102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>775207</t>
+          <t>775252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16070</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368223</t>
+          <t>368873</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376263</t>
+          <t>376278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360225</t>
+          <t>360277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369461</t>
+          <t>370249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>733430</t>
+          <t>732436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744787</t>
+          <t>745347</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>16560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508074</t>
+          <t>508837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520286</t>
+          <t>519848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156060</t>
+          <t>155706</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669806</t>
+          <t>671476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>684823</t>
+          <t>684926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17617</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32485</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1128811</t>
+          <t>1126160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144088</t>
+          <t>1143445</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808259</t>
+          <t>808976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821000</t>
+          <t>821112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1943029</t>
+          <t>1942337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1962786</t>
+          <t>1963067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17655</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16837</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29857</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>603051</t>
+          <t>602116</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>616495</t>
+          <t>616160</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>721407</t>
+          <t>721918</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>733559</t>
+          <t>733637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1329093</t>
+          <t>1330429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1347828</t>
+          <t>1348102</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280661</t>
+          <t>281319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1062370</t>
+          <t>1063315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1076913</t>
+          <t>1077179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1348224</t>
+          <t>1347783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1362774</t>
+          <t>1363051</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>23001</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48859</t>
+          <t>48689</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51295</t>
+          <t>52401</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56144</t>
+          <t>55780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91710</t>
+          <t>91935</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3336863</t>
+          <t>3337033</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3362235</t>
+          <t>3362721</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3480301</t>
+          <t>3479195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3505317</t>
+          <t>3505151</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6825608</t>
+          <t>6825383</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6861174</t>
+          <t>6861538</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>15340</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28018</t>
+          <t>28729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>488111</t>
+          <t>486695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>500338</t>
+          <t>499484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>432280</t>
+          <t>432127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>442055</t>
+          <t>441999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>924661</t>
+          <t>923950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>940151</t>
+          <t>939666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>22220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>13248</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32308</t>
+          <t>32195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430060</t>
+          <t>429993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>445314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367079</t>
+          <t>368109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>378283</t>
+          <t>378022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>802485</t>
+          <t>802598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821026</t>
+          <t>821545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25041</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35633</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643223</t>
+          <t>641273</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665186</t>
+          <t>664623</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150312</t>
+          <t>149675</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163819</t>
+          <t>163774</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>799542</t>
+          <t>800140</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827703</t>
+          <t>827743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34791</t>
+          <t>35442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19122</t>
+          <t>18952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>590596</t>
+          <t>518310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41729</t>
+          <t>41542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>757435</t>
+          <t>819284</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1000028</t>
+          <t>999377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1019523</t>
+          <t>1019050</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>387498</t>
+          <t>459784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>958972</t>
+          <t>959142</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1255477</t>
+          <t>1193628</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1971183</t>
+          <t>1971370</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24995</t>
+          <t>24612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24313</t>
+          <t>23427</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45145</t>
+          <t>45280</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37532</t>
+          <t>37370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62150</t>
+          <t>62792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>450051</t>
+          <t>450434</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466943</t>
+          <t>467129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>796190</t>
+          <t>796055</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>817022</t>
+          <t>817908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1254231</t>
+          <t>1253589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1278849</t>
+          <t>1279011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>296</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31861</t>
+          <t>31459</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>18662</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34318</t>
+          <t>34062</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236295</t>
+          <t>235484</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240350</t>
+          <t>240211</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>729510</t>
+          <t>729912</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>743885</t>
+          <t>744052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>967560</t>
+          <t>967816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>983358</t>
+          <t>983216</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55439</t>
+          <t>56748</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96217</t>
+          <t>95418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99391</t>
+          <t>100983</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>910690</t>
+          <t>929866</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>172232</t>
+          <t>172038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1041230</t>
+          <t>1079339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3279843</t>
+          <t>3280642</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3320621</t>
+          <t>3319312</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2667068</t>
+          <t>2647892</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3478367</t>
+          <t>3476775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5912588</t>
+          <t>5874479</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6781586</t>
+          <t>6781780</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_senso_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>459940</t>
+          <t>460034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471164</t>
+          <t>471352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293347</t>
+          <t>293874</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303766</t>
+          <t>303886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758767</t>
+          <t>759239</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773438</t>
+          <t>773405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353754</t>
+          <t>353400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364074</t>
+          <t>364116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363716</t>
+          <t>363588</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370950</t>
+          <t>370933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>721158</t>
+          <t>721887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733811</t>
+          <t>734019</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14624</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531350</t>
+          <t>531884</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540520</t>
+          <t>540521</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159232</t>
+          <t>159882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>166841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>695547</t>
+          <t>693571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>706954</t>
+          <t>706411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32976</t>
+          <t>32003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47372</t>
+          <t>44571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1205358</t>
+          <t>1206331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1224515</t>
+          <t>1224426</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>696279</t>
+          <t>695669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>709056</t>
+          <t>709098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1905248</t>
+          <t>1908049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1929350</t>
+          <t>1930118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>13653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>334054</t>
+          <t>333969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346776</t>
+          <t>346155</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>554399</t>
+          <t>555099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>565587</t>
+          <t>565733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>894628</t>
+          <t>894370</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>910651</t>
+          <t>910555</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,44 +2468,44 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>25288</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>16742</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>36577</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>2,93%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>25288</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>16248</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>37256</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40164</t>
+          <t>39101</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289452</t>
+          <t>289809</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,47 +2576,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1223472</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1212183</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1232018</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>97,97%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>97,07%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1223472</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1211504</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1232512</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1506796</t>
+          <t>1507859</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1528386</t>
+          <t>1528978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37639</t>
+          <t>38793</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67095</t>
+          <t>65808</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42920</t>
+          <t>42996</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74087</t>
+          <t>72290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87079</t>
+          <t>89680</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130229</t>
+          <t>130570</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3203095</t>
+          <t>3204382</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3232551</t>
+          <t>3231397</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3304037</t>
+          <t>3305834</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3335204</t>
+          <t>3335128</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6518085</t>
+          <t>6517744</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6561235</t>
+          <t>6558634</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16413</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18722</t>
+          <t>18613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10266</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>29785</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420798</t>
+          <t>421006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434112</t>
+          <t>434176</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295732</t>
+          <t>295841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310171</t>
+          <t>309887</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>722379</t>
+          <t>721880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741399</t>
+          <t>741955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13284</t>
+          <t>13909</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411417</t>
+          <t>410515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418026</t>
+          <t>417943</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327598</t>
+          <t>327532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336915</t>
+          <t>336956</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>743524</t>
+          <t>742899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>753862</t>
+          <t>753732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23334</t>
+          <t>22870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30612</t>
+          <t>29437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>606081</t>
+          <t>606545</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623099</t>
+          <t>622728</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246928</t>
+          <t>248313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257272</t>
+          <t>258086</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>858932</t>
+          <t>860107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878197</t>
+          <t>878539</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33980</t>
+          <t>34829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>29487</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28486</t>
+          <t>29469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56428</t>
+          <t>56186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1125029</t>
+          <t>1124180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144553</t>
+          <t>1144839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>737194</t>
+          <t>737170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>755341</t>
+          <t>756071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1869239</t>
+          <t>1869481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897181</t>
+          <t>1896198</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30520</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>498973</t>
+          <t>498244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508534</t>
+          <t>508558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>737279</t>
+          <t>737351</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>753305</t>
+          <t>753773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1241598</t>
+          <t>1241611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1260026</t>
+          <t>1260509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13849</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35612</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18741</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40648</t>
+          <t>40231</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253033</t>
+          <t>253232</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264958</t>
+          <t>265007</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1073739</t>
+          <t>1074590</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1094113</t>
+          <t>1094132</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1335585</t>
+          <t>1336002</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357492</t>
+          <t>1357463</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>43411</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76591</t>
+          <t>75514</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59959</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94752</t>
+          <t>94656</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112766</t>
+          <t>109470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>159654</t>
+          <t>159167</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3345319</t>
+          <t>3346396</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3378279</t>
+          <t>3378499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3455373</t>
+          <t>3455469</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3490166</t>
+          <t>3491692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6812381</t>
+          <t>6812868</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6859269</t>
+          <t>6862565</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422042</t>
+          <t>421895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428310</t>
+          <t>428309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>342405</t>
+          <t>342575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>768102</t>
+          <t>767191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>775252</t>
+          <t>775244</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368873</t>
+          <t>368792</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376278</t>
+          <t>376275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360277</t>
+          <t>359847</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370249</t>
+          <t>370217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>732436</t>
+          <t>733346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745347</t>
+          <t>745369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508837</t>
+          <t>508056</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519848</t>
+          <t>519886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155706</t>
+          <t>152006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671476</t>
+          <t>670959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>684926</t>
+          <t>684823</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33177</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1126160</t>
+          <t>1126444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1143445</t>
+          <t>1144250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808976</t>
+          <t>808107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821112</t>
+          <t>820995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1942337</t>
+          <t>1942714</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1963067</t>
+          <t>1962575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18590</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>17188</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28521</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>602116</t>
+          <t>602335</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>616160</t>
+          <t>616494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>721918</t>
+          <t>721056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>733637</t>
+          <t>733565</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1330429</t>
+          <t>1329622</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1348102</t>
+          <t>1347614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,47 +7768,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>12119</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>6220</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>19918</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>12119</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>6119</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>21387</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281319</t>
+          <t>280443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1063315</t>
+          <t>1063855</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1077179</t>
+          <t>1077429</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1347783</t>
+          <t>1349252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1363051</t>
+          <t>1362950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23001</t>
+          <t>24151</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48689</t>
+          <t>49838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26445</t>
+          <t>26971</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52401</t>
+          <t>53624</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55780</t>
+          <t>57049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91935</t>
+          <t>92008</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3337033</t>
+          <t>3335884</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3362721</t>
+          <t>3361571</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3479195</t>
+          <t>3477972</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3505151</t>
+          <t>3504625</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6825383</t>
+          <t>6825310</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6861538</t>
+          <t>6860269</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>14313</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>495194</t>
+          <t>539748</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>486695</t>
+          <t>531428</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>499484</t>
+          <t>544694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>438157</t>
+          <t>477456</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>432127</t>
+          <t>471572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>441999</t>
+          <t>481835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>933351</t>
+          <t>1017204</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>923950</t>
+          <t>1008644</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>939666</t>
+          <t>1024716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,17 +8976,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22220</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20713</t>
+          <t>22673</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>14267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32195</t>
+          <t>35285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -9089,17 +9089,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>439720</t>
+          <t>469870</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>429993</t>
+          <t>459408</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445314</t>
+          <t>475667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>374360</t>
+          <t>413812</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368109</t>
+          <t>406345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>378022</t>
+          <t>417957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>814080</t>
+          <t>883682</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>802598</t>
+          <t>871070</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821545</t>
+          <t>892088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26991</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>22795</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35035</t>
+          <t>36404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>654861</t>
+          <t>457017</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641273</t>
+          <t>447901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664623</t>
+          <t>463431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159950</t>
+          <t>179297</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149675</t>
+          <t>166463</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163774</t>
+          <t>183915</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>814810</t>
+          <t>636314</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>800140</t>
+          <t>622705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827743</t>
+          <t>644490</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15769</t>
+          <t>19535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35442</t>
+          <t>43338</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>222245</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18952</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>518310</t>
+          <t>26425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>246141</t>
+          <t>48840</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>36633</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>819284</t>
+          <t>66106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1010923</t>
+          <t>1102438</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>999377</t>
+          <t>1088505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1019050</t>
+          <t>1112308</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>755849</t>
+          <t>841777</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>459784</t>
+          <t>834786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>959142</t>
+          <t>847549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1766771</t>
+          <t>1944214</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1193628</t>
+          <t>1926948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1971370</t>
+          <t>1956421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>8082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34369</t>
+          <t>38276</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23427</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45280</t>
+          <t>47817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>48612</t>
+          <t>53739</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37370</t>
+          <t>42695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62792</t>
+          <t>68074</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>460803</t>
+          <t>552501</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>450434</t>
+          <t>544236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467129</t>
+          <t>559882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>806966</t>
+          <t>792574</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>796055</t>
+          <t>783033</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>817908</t>
+          <t>801233</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1267769</t>
+          <t>1345075</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1253589</t>
+          <t>1330740</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1279011</t>
+          <t>1356119</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>537</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>29637</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31459</t>
+          <t>40322</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25016</t>
+          <t>32665</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18662</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34062</t>
+          <t>45273</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239139</t>
+          <t>234200</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235484</t>
+          <t>226017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240211</t>
+          <t>236691</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>737724</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>729912</t>
+          <t>803959</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>744052</t>
+          <t>823470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>976862</t>
+          <t>1048844</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>967816</t>
+          <t>1036236</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>983216</t>
+          <t>1058318</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>75422</t>
+          <t>86703</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56748</t>
+          <t>69300</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95418</t>
+          <t>109197</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>304753</t>
+          <t>115833</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100983</t>
+          <t>97927</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>929866</t>
+          <t>135229</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>380175</t>
+          <t>202537</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>172038</t>
+          <t>176806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1079339</t>
+          <t>227882</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3300638</t>
+          <t>3355773</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3280642</t>
+          <t>3333279</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3319312</t>
+          <t>3373176</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3273005</t>
+          <t>3519560</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2647892</t>
+          <t>3500164</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3476775</t>
+          <t>3537466</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6573643</t>
+          <t>6875332</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5874479</t>
+          <t>6849987</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6781780</t>
+          <t>6901063</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_senso_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
